--- a/july 2026/GT_JULY_26/09-07-2026/Furqan.xlsx
+++ b/july 2026/GT_JULY_26/09-07-2026/Furqan.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55EDBE09-1D43-4353-8696-E564BB8FD4B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48027426-F3E8-4F72-933F-F2B5B1D39F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3244,7 +3244,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -3272,7 +3272,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -4465,7 +4465,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -4493,7 +4493,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -5686,7 +5686,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -5714,7 +5714,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -6907,7 +6907,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -6935,7 +6935,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -8128,7 +8128,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -8156,7 +8156,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -9349,7 +9349,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -9377,7 +9377,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -10567,7 +10567,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -10595,7 +10595,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -11784,7 +11784,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -11812,7 +11812,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -13001,7 +13001,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -13029,7 +13029,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -14218,7 +14218,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -14246,7 +14246,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -18185,7 +18185,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -18213,7 +18213,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -19402,7 +19402,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -19430,7 +19430,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -20619,7 +20619,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -20647,7 +20647,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -21836,7 +21836,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -21864,7 +21864,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -23058,7 +23058,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -23086,7 +23086,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -24643,7 +24643,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -24671,7 +24671,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -26147,7 +26147,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -26175,7 +26175,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -27370,7 +27370,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -27398,7 +27398,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -28602,7 +28602,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -28630,7 +28630,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -29825,7 +29825,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -29853,7 +29853,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -31046,7 +31046,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -31074,7 +31074,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
